--- a/src/formats/FORMATO_RECORRIDO_NEW.xlsx
+++ b/src/formats/FORMATO_RECORRIDO_NEW.xlsx
@@ -75,31 +75,67 @@
     <t xml:space="preserve">1002035861</t>
   </si>
   <si>
+    <t xml:space="preserve">Incumplimiento BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal con barba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARCIA QUITERIO GABRIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acto inseguro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juego o bromas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uso de pulseras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violencia/ bandalismo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingreso de dulces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de uso de EPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARRIETA MOSQUEDA OMAR ALFONSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinador de Seguridad y Salud en el T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uso de anillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALFONSO MARTINEZ GARCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPERADOR DE MANTENIMIENTO ELECTRICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1066743313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uso incorrecto de los materiales</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unas largas</t>
   </si>
   <si>
-    <t xml:space="preserve">Uso incorrecto de los materiales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GARCIA QUITERIO GABRIEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALVAREZ ESQUIVEL ELSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personal con barba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juego o bromas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Falta de permiso de trabajo</t>
+    <t xml:space="preserve">Bata sin abrochar</t>
   </si>
 </sst>
 </file>
@@ -1236,19 +1272,19 @@
         <v>2</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>10</v>
       </c>
       <c r="D8" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s" s="2">
         <v>17</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>19</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" t="s" s="2">
@@ -1272,10 +1308,10 @@
         <v>11</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" t="s" s="2">
@@ -1286,81 +1322,193 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="A10" s="2">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="H10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="A11" s="2">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>22</v>
+      </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="H11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="A12" s="2">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="H12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="A13" s="2">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>30</v>
+      </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="H13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="A14" s="2">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>22</v>
+      </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="H14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="A15" s="2">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>22</v>
+      </c>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
+      <c r="H15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="A16" s="2">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>22</v>
+      </c>
       <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
+      <c r="H16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="14.25" customHeight="1">
       <c r="A17" s="2"/>
